--- a/example/master_table.xlsx
+++ b/example/master_table.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\ExcelAutoTool\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="2126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="2236">
   <si>
     <t>DSGY-F704JBKZ</t>
   </si>
@@ -5784,9 +5784,6 @@
     <t>STAND_POST</t>
   </si>
   <si>
-    <t>IC_</t>
-  </si>
-  <si>
     <t>JOG_KEY_UNIT</t>
   </si>
   <si>
@@ -6096,7 +6093,391 @@
     <t>*</t>
   </si>
   <si>
-    <t>garis / line</t>
+    <t>BLANK</t>
+  </si>
+  <si>
+    <t>X ADA GAMBAR</t>
+  </si>
+  <si>
+    <t>MATI</t>
+  </si>
+  <si>
+    <t>TIDAK BISA HIDUP</t>
+  </si>
+  <si>
+    <t>TIDAK BS HIDUP</t>
+  </si>
+  <si>
+    <t>LOGO</t>
+  </si>
+  <si>
+    <t>HDMI</t>
+  </si>
+  <si>
+    <t>SIARAN</t>
+  </si>
+  <si>
+    <t>CHANNEL</t>
+  </si>
+  <si>
+    <t>Diff Month</t>
+  </si>
+  <si>
+    <t>0-12</t>
+  </si>
+  <si>
+    <t>&lt; 1 Year</t>
+  </si>
+  <si>
+    <t>13-24</t>
+  </si>
+  <si>
+    <t>1 - 2 Years</t>
+  </si>
+  <si>
+    <t>25-36</t>
+  </si>
+  <si>
+    <t>2 - 3 Years</t>
+  </si>
+  <si>
+    <t>=&gt;37</t>
+  </si>
+  <si>
+    <t>&gt; 3 Years</t>
+  </si>
+  <si>
+    <t>Panel Usage</t>
+  </si>
+  <si>
+    <t>init</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>CIDENG</t>
+  </si>
+  <si>
+    <t>JAKARTA</t>
+  </si>
+  <si>
+    <t>PULOGADUNG</t>
+  </si>
+  <si>
+    <t>JAKARTA SELATAN</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>repair_comment</t>
+  </si>
+  <si>
+    <t>ZY</t>
+  </si>
+  <si>
+    <t>*ext</t>
+  </si>
+  <si>
+    <t>UPGRADE</t>
+  </si>
+  <si>
+    <t>*factor</t>
+  </si>
+  <si>
+    <t>JELAS</t>
+  </si>
+  <si>
+    <t>BATAL</t>
+  </si>
+  <si>
+    <t>Repair Action</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Defect</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Repair LVDS</t>
+  </si>
+  <si>
+    <t>Reinsert Speaker</t>
+  </si>
+  <si>
+    <t>Subtitusi</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Replace Panel - Before Change</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Replace Panel</t>
+  </si>
+  <si>
+    <t>Repair Panel</t>
+  </si>
+  <si>
+    <t>Replace Main Unit</t>
+  </si>
+  <si>
+    <t>Repair Main Unit</t>
+  </si>
+  <si>
+    <t>Replace Power Unit</t>
+  </si>
+  <si>
+    <t>Replace TCON</t>
+  </si>
+  <si>
+    <t>Repair Power Unit</t>
+  </si>
+  <si>
+    <t>Factory Reset</t>
+  </si>
+  <si>
+    <t>Upgrade</t>
+  </si>
+  <si>
+    <t>Reinsert LVDS</t>
+  </si>
+  <si>
+    <t>Repair IR Unit</t>
+  </si>
+  <si>
+    <t>Repair LED BAR</t>
+  </si>
+  <si>
+    <t>Repair Speaker</t>
+  </si>
+  <si>
+    <t>Replace Speaker</t>
+  </si>
+  <si>
+    <t>Replace Led Bar</t>
+  </si>
+  <si>
+    <t>Replace IR Unit</t>
+  </si>
+  <si>
+    <t>Replace Wifi Unit</t>
+  </si>
+  <si>
+    <t>Repair TCON</t>
+  </si>
+  <si>
+    <t>Repair Wifi Unit</t>
+  </si>
+  <si>
+    <t>Reinsert Wifi Unit</t>
+  </si>
+  <si>
+    <t>Reinsert Cabinet</t>
+  </si>
+  <si>
+    <t>Reinsert Socket</t>
+  </si>
+  <si>
+    <t>Replace Remote</t>
+  </si>
+  <si>
+    <t>Repair Remote</t>
+  </si>
+  <si>
+    <t>Replace Tape</t>
+  </si>
+  <si>
+    <t>Verified OK</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>Before Improve - Remote</t>
+  </si>
+  <si>
+    <t>Before Improve</t>
+  </si>
+  <si>
+    <t>TOTAL_OFF</t>
+  </si>
+  <si>
+    <t>LINE</t>
+  </si>
+  <si>
+    <t>STANDBY</t>
+  </si>
+  <si>
+    <t>LOGO_FREEZE</t>
+  </si>
+  <si>
+    <t>HDMI_NG</t>
+  </si>
+  <si>
+    <t>NO_CHANNEL</t>
+  </si>
+  <si>
+    <t>*garis*</t>
+  </si>
+  <si>
+    <t>*line*</t>
+  </si>
+  <si>
+    <t>*GOYANG*</t>
+  </si>
+  <si>
+    <t>*BAYANG*</t>
+  </si>
+  <si>
+    <t>BLUR</t>
+  </si>
+  <si>
+    <t>DOT</t>
+  </si>
+  <si>
+    <t>*DOT*</t>
+  </si>
+  <si>
+    <t>*BERGERAK*</t>
+  </si>
+  <si>
+    <t>*SETENGAH*</t>
+  </si>
+  <si>
+    <t>HALF</t>
+  </si>
+  <si>
+    <t>*RUSAK PANEL*</t>
+  </si>
+  <si>
+    <t>BROKEN</t>
+  </si>
+  <si>
+    <t>*BURAM*</t>
+  </si>
+  <si>
+    <t>MURA</t>
+  </si>
+  <si>
+    <t>*PIXEL*</t>
+  </si>
+  <si>
+    <t>*GAMBAR TDK KELUAR*</t>
+  </si>
+  <si>
+    <t>*BLANK*</t>
+  </si>
+  <si>
+    <t>NO_PICTURE</t>
+  </si>
+  <si>
+    <t>TDK ADA GAMABAR</t>
+  </si>
+  <si>
+    <t>TIDAK AD AGAMBAR</t>
+  </si>
+  <si>
+    <t>TIDAK AD GAMBAR</t>
+  </si>
+  <si>
+    <t>*TIDAK BISA HIDUP*</t>
+  </si>
+  <si>
+    <t>*STANDBY*</t>
+  </si>
+  <si>
+    <t>*STAND BY*</t>
+  </si>
+  <si>
+    <t>*STANBY*</t>
+  </si>
+  <si>
+    <t>*MATOT*</t>
+  </si>
+  <si>
+    <t>*MATOL*</t>
+  </si>
+  <si>
+    <t>LAYAR BLANK</t>
+  </si>
+  <si>
+    <t>*TDK ADA GAMBAR*</t>
+  </si>
+  <si>
+    <t>*TIDAK ADA GAMBAR*</t>
+  </si>
+  <si>
+    <t>ERROR</t>
+  </si>
+  <si>
+    <t>*NETFLIX*</t>
+  </si>
+  <si>
+    <t>*MATI*</t>
+  </si>
+  <si>
+    <t>SIGNAL</t>
+  </si>
+  <si>
+    <t>SINYAL</t>
+  </si>
+  <si>
+    <t>INDIKATOR</t>
+  </si>
+  <si>
+    <t>PROTECT</t>
+  </si>
+  <si>
+    <t>REMOT</t>
+  </si>
+  <si>
+    <t>SENSOR_NG</t>
+  </si>
+  <si>
+    <t>REMOTE</t>
+  </si>
+  <si>
+    <t>SENSOR</t>
+  </si>
+  <si>
+    <t>TIDAK ADA SUARA</t>
+  </si>
+  <si>
+    <t>CHANEL</t>
+  </si>
+  <si>
+    <t>SOUND_NG</t>
+  </si>
+  <si>
+    <t>TOMBOL</t>
+  </si>
+  <si>
+    <t>BUTTON_NG</t>
+  </si>
+  <si>
+    <t>EROR</t>
   </si>
   <si>
     <t>TIDAK ADA GAMBAR</t>
@@ -6105,313 +6486,262 @@
     <t>TDK ADA GAMBAR</t>
   </si>
   <si>
-    <t>BLANK</t>
-  </si>
-  <si>
-    <t>X ADA GAMBAR</t>
-  </si>
-  <si>
-    <t>MATI</t>
-  </si>
-  <si>
-    <t>HANYA SUARA SAJA</t>
-  </si>
-  <si>
-    <t>TIDAK BISA HIDUP</t>
-  </si>
-  <si>
-    <t>TIDAK BS HIDUP</t>
-  </si>
-  <si>
-    <t>STANDBY / STAND BY</t>
-  </si>
-  <si>
-    <t>LOGO</t>
-  </si>
-  <si>
-    <t>HDMI</t>
-  </si>
-  <si>
-    <t>SIARAN</t>
-  </si>
-  <si>
-    <t>SIGNAL / SINYAL</t>
-  </si>
-  <si>
-    <t>CHANNEL</t>
-  </si>
-  <si>
-    <t>Diff Month</t>
-  </si>
-  <si>
-    <t>0-12</t>
-  </si>
-  <si>
-    <t>&lt; 1 Year</t>
-  </si>
-  <si>
-    <t>13-24</t>
-  </si>
-  <si>
-    <t>1 - 2 Years</t>
-  </si>
-  <si>
-    <t>25-36</t>
-  </si>
-  <si>
-    <t>2 - 3 Years</t>
-  </si>
-  <si>
-    <t>=&gt;37</t>
-  </si>
-  <si>
-    <t>&gt; 3 Years</t>
-  </si>
-  <si>
-    <t>Panel Usage</t>
-  </si>
-  <si>
-    <t>init</t>
-  </si>
-  <si>
-    <t>branch</t>
-  </si>
-  <si>
-    <t>CIDENG</t>
-  </si>
-  <si>
-    <t>JAKARTA</t>
-  </si>
-  <si>
-    <t>PULOGADUNG</t>
-  </si>
-  <si>
-    <t>JAKARTA SELATAN</t>
-  </si>
-  <si>
-    <t>action</t>
-  </si>
-  <si>
-    <t>replace_power_unit</t>
-  </si>
-  <si>
-    <t>replace_panel</t>
-  </si>
-  <si>
-    <t>replace_main_unit</t>
-  </si>
-  <si>
-    <t>Remote Control</t>
-  </si>
-  <si>
-    <t>replace_remote_control</t>
-  </si>
-  <si>
-    <t>repair_comment</t>
-  </si>
-  <si>
-    <t>*bawa</t>
-  </si>
-  <si>
-    <t>ZY</t>
-  </si>
-  <si>
-    <t>*ext</t>
-  </si>
-  <si>
-    <t>external</t>
-  </si>
-  <si>
-    <t>UPGRADE</t>
-  </si>
-  <si>
-    <t>upgrade</t>
-  </si>
-  <si>
-    <t>*factor</t>
-  </si>
-  <si>
-    <t>factory_reset</t>
-  </si>
-  <si>
-    <t>JELAS</t>
-  </si>
-  <si>
-    <t>explanation</t>
-  </si>
-  <si>
-    <t>BATAL</t>
-  </si>
-  <si>
-    <t>cancel</t>
-  </si>
-  <si>
-    <t>Repair Action</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Defect</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Repair LVDS</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Reinsert Speaker</t>
-  </si>
-  <si>
-    <t>Subtitusi</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Replace Panel - Before Change</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Non Defect</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Replace Panel</t>
-  </si>
-  <si>
-    <t>Panel</t>
-  </si>
-  <si>
-    <t>Repair Panel</t>
-  </si>
-  <si>
-    <t>Replace Main Unit</t>
-  </si>
-  <si>
-    <t>Main Unit</t>
-  </si>
-  <si>
-    <t>Repair Main Unit</t>
-  </si>
-  <si>
-    <t>Replace Power Unit</t>
-  </si>
-  <si>
-    <t>Power Unit</t>
-  </si>
-  <si>
-    <t>Replace TCON</t>
-  </si>
-  <si>
-    <t>Repair Power Unit</t>
-  </si>
-  <si>
-    <t>Factory Reset</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Upgrade</t>
-  </si>
-  <si>
-    <t>Reinsert LVDS</t>
-  </si>
-  <si>
-    <t>Repair IR Unit</t>
-  </si>
-  <si>
-    <t>Repair LED BAR</t>
-  </si>
-  <si>
-    <t>Repair Speaker</t>
-  </si>
-  <si>
-    <t>Replace Speaker</t>
-  </si>
-  <si>
-    <t>Replace Led Bar</t>
-  </si>
-  <si>
-    <t>Replace LVDS</t>
-  </si>
-  <si>
-    <t>Replace IR Unit</t>
-  </si>
-  <si>
-    <t>Replace Wifi Unit</t>
-  </si>
-  <si>
-    <t>Repair TCON</t>
-  </si>
-  <si>
-    <t>Repair Wifi Unit</t>
-  </si>
-  <si>
-    <t>Reinsert Wifi Unit</t>
-  </si>
-  <si>
-    <t>Reinsert Cabinet</t>
-  </si>
-  <si>
-    <t>Reinsert Socket</t>
-  </si>
-  <si>
-    <t>Replace Remote</t>
-  </si>
-  <si>
-    <t>Repair Remote</t>
-  </si>
-  <si>
-    <t>Replace Tape</t>
-  </si>
-  <si>
-    <t>Verified OK</t>
-  </si>
-  <si>
-    <t>Cancel</t>
-  </si>
-  <si>
-    <t>External</t>
-  </si>
-  <si>
-    <t>Before Improve - Remote</t>
-  </si>
-  <si>
-    <t>Before Improve</t>
-  </si>
-  <si>
-    <t>TOTAL_OFF</t>
-  </si>
-  <si>
-    <t>LINE</t>
-  </si>
-  <si>
-    <t>STANDBY</t>
-  </si>
-  <si>
-    <t>LOGO_FREEZE</t>
-  </si>
-  <si>
-    <t>HDMI_NG</t>
-  </si>
-  <si>
-    <t>NO_CHANNEL</t>
+    <t>TIDAK ADA SIARAN</t>
+  </si>
+  <si>
+    <t>DOMINAN</t>
+  </si>
+  <si>
+    <t>MERAH</t>
+  </si>
+  <si>
+    <t>PUTIH</t>
+  </si>
+  <si>
+    <t>SEBELAH</t>
+  </si>
+  <si>
+    <t>NO DISPLAY</t>
+  </si>
+  <si>
+    <t>PECAH</t>
+  </si>
+  <si>
+    <t>RC_NG</t>
+  </si>
+  <si>
+    <t>DISPLAY_NG</t>
+  </si>
+  <si>
+    <t>GELAP</t>
+  </si>
+  <si>
+    <t>HANYA SUARA</t>
+  </si>
+  <si>
+    <t>SUARA SAJA</t>
+  </si>
+  <si>
+    <t>LAYAR BERMASALAH</t>
+  </si>
+  <si>
+    <t>LAYAR BLUE SCREEN</t>
+  </si>
+  <si>
+    <t>LAYAR REDUP DAN WARNA UNGU</t>
+  </si>
+  <si>
+    <t>ANTENE</t>
+  </si>
+  <si>
+    <t>LAYAR MERAH</t>
+  </si>
+  <si>
+    <t>PICTURE_NG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIDAK NYALA </t>
+  </si>
+  <si>
+    <t>TIDAK BISA NYALA</t>
+  </si>
+  <si>
+    <t>KLISE</t>
+  </si>
+  <si>
+    <t>EXTERNAL</t>
+  </si>
+  <si>
+    <t>CANCEL</t>
+  </si>
+  <si>
+    <t>REPLACE_POWER_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_PANEL</t>
+  </si>
+  <si>
+    <t>REPLACE_MAIN_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_REMOTE_CONTROL</t>
+  </si>
+  <si>
+    <t>FACTORY_RESET</t>
+  </si>
+  <si>
+    <t>EXPLANATION</t>
+  </si>
+  <si>
+    <t>REPAIR_POWER_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_LED_BAR</t>
+  </si>
+  <si>
+    <t>REPLACE_LVDS_WIRE</t>
+  </si>
+  <si>
+    <t>REPLACE_AC_CORD</t>
+  </si>
+  <si>
+    <t>REPLACE_FFC_WIRE</t>
+  </si>
+  <si>
+    <t>CARRY</t>
+  </si>
+  <si>
+    <t>RESOLDERING PSU</t>
+  </si>
+  <si>
+    <t>UNIT CEK OK</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>PERBAIKI MAIN UNIT</t>
+  </si>
+  <si>
+    <t>REPAIR_MAIN_UNIT</t>
+  </si>
+  <si>
+    <t>RESET PROGRAM</t>
+  </si>
+  <si>
+    <t>SETTING</t>
+  </si>
+  <si>
+    <t>bawa</t>
+  </si>
+  <si>
+    <t>UPDATE</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
+  </si>
+  <si>
+    <t>ACC BIAYA</t>
+  </si>
+  <si>
+    <t>REPAIR MAIN</t>
+  </si>
+  <si>
+    <t>REPAIR POWER</t>
+  </si>
+  <si>
+    <t>RESOLDERING MAIN</t>
+  </si>
+  <si>
+    <t>RESOLDERING MB</t>
+  </si>
+  <si>
+    <t>SET UP DATA</t>
+  </si>
+  <si>
+    <t>RESOLDERING IC7801</t>
+  </si>
+  <si>
+    <t>CEK FUNGSI OK</t>
+  </si>
+  <si>
+    <t>RISET PROGRAM</t>
+  </si>
+  <si>
+    <t>RESET-ULANG</t>
+  </si>
+  <si>
+    <t>PERBAIKAN POWER</t>
+  </si>
+  <si>
+    <t>PERBAIKAN MODUL POWER</t>
+  </si>
+  <si>
+    <t>EXS</t>
+  </si>
+  <si>
+    <t>RESOLDER PCB MAIN</t>
+  </si>
+  <si>
+    <t>RESOLDRING D7801</t>
+  </si>
+  <si>
+    <t>SERVICE MODE</t>
+  </si>
+  <si>
+    <t>CEK OK</t>
+  </si>
+  <si>
+    <t>TO WS</t>
+  </si>
+  <si>
+    <t>PERBAIKI POWER</t>
+  </si>
+  <si>
+    <t>PERBAIKAN MAIN</t>
+  </si>
+  <si>
+    <t>BERSIHKAN</t>
+  </si>
+  <si>
+    <t>KOTOR</t>
+  </si>
+  <si>
+    <t>RESET PABRIK</t>
+  </si>
+  <si>
+    <t>SOLDERING MAIN</t>
+  </si>
+  <si>
+    <t>DEFECT</t>
+  </si>
+  <si>
+    <t>NON DEFECT</t>
+  </si>
+  <si>
+    <t>MAIN UNIT</t>
+  </si>
+  <si>
+    <t>POWER UNIT</t>
+  </si>
+  <si>
+    <t>SOFTWARE</t>
+  </si>
+  <si>
+    <t>STEL ULANG PROGRAM</t>
+  </si>
+  <si>
+    <t>TEST FUNGSI</t>
+  </si>
+  <si>
+    <t>SOLDER MAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESOLDERING MODUL </t>
+  </si>
+  <si>
+    <t>REPAIR PWB MAIN</t>
+  </si>
+  <si>
+    <t>REPAIR REGULATOR</t>
+  </si>
+  <si>
+    <t>REPAIR REMOTE</t>
+  </si>
+  <si>
+    <t>REPAIR_REMOTE</t>
+  </si>
+  <si>
+    <t>RESTAR PROGRAM</t>
+  </si>
+  <si>
+    <t>TDK ACC</t>
+  </si>
+  <si>
+    <t>RESET UNIT</t>
+  </si>
+  <si>
+    <t>RESET ULANG</t>
   </si>
 </sst>
 </file>
@@ -6421,7 +6751,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6520,6 +6850,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -6609,7 +6943,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6706,6 +7040,13 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7173,7 +7514,7 @@
         <v>956</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7189,7 +7530,7 @@
         <v>954</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7197,7 +7538,7 @@
         <v>1626</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7205,7 +7546,7 @@
         <v>1320</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7213,7 +7554,7 @@
         <v>953</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7221,7 +7562,7 @@
         <v>1774</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7229,7 +7570,7 @@
         <v>1025</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7293,7 +7634,7 @@
         <v>949</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7301,7 +7642,7 @@
         <v>948</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7685,7 +8026,7 @@
         <v>900</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7693,7 +8034,7 @@
         <v>901</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7701,7 +8042,7 @@
         <v>905</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7709,7 +8050,7 @@
         <v>902</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7717,7 +8058,7 @@
         <v>903</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7725,7 +8066,7 @@
         <v>897</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7733,7 +8074,7 @@
         <v>898</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7741,7 +8082,7 @@
         <v>899</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8133,7 +8474,7 @@
         <v>868</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8141,7 +8482,7 @@
         <v>869</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8149,7 +8490,7 @@
         <v>1398</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8285,7 +8626,7 @@
         <v>1779</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -9101,7 +9442,7 @@
         <v>814</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9325,7 +9666,7 @@
         <v>1147</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -9333,7 +9674,7 @@
         <v>1355</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -9341,7 +9682,7 @@
         <v>1356</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -10237,7 +10578,7 @@
         <v>1039</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -14093,7 +14434,7 @@
         <v>1394</v>
       </c>
       <c r="B884" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -14101,7 +14442,7 @@
         <v>1464</v>
       </c>
       <c r="B885" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -14109,7 +14450,7 @@
         <v>1471</v>
       </c>
       <c r="B886" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -14117,7 +14458,7 @@
         <v>1467</v>
       </c>
       <c r="B887" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -14125,7 +14466,7 @@
         <v>1472</v>
       </c>
       <c r="B888" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -14133,7 +14474,7 @@
         <v>1469</v>
       </c>
       <c r="B889" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -14141,7 +14482,7 @@
         <v>1473</v>
       </c>
       <c r="B890" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -14149,7 +14490,7 @@
         <v>1476</v>
       </c>
       <c r="B891" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -14157,7 +14498,7 @@
         <v>1482</v>
       </c>
       <c r="B892" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -14165,7 +14506,7 @@
         <v>1478</v>
       </c>
       <c r="B893" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -14173,7 +14514,7 @@
         <v>1483</v>
       </c>
       <c r="B894" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -14181,7 +14522,7 @@
         <v>1480</v>
       </c>
       <c r="B895" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -14189,7 +14530,7 @@
         <v>1484</v>
       </c>
       <c r="B896" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -14197,7 +14538,7 @@
         <v>1400</v>
       </c>
       <c r="B897" s="3" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -17810,7 +18151,7 @@
         <v>271</v>
       </c>
       <c r="B1347" s="3" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1348" spans="1:2">
@@ -17834,7 +18175,7 @@
         <v>268</v>
       </c>
       <c r="B1350" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1351" spans="1:2">
@@ -17842,7 +18183,7 @@
         <v>1319</v>
       </c>
       <c r="B1351" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1352" spans="1:2">
@@ -17850,7 +18191,7 @@
         <v>1331</v>
       </c>
       <c r="B1352" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1353" spans="1:2">
@@ -19618,7 +19959,7 @@
         <v>1188</v>
       </c>
       <c r="B1573" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1574" spans="1:2">
@@ -19626,7 +19967,7 @@
         <v>1422</v>
       </c>
       <c r="B1574" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1575" spans="1:2">
@@ -19634,7 +19975,7 @@
         <v>1421</v>
       </c>
       <c r="B1575" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1576" spans="1:2">
@@ -20762,7 +21103,7 @@
         <v>39</v>
       </c>
       <c r="B1716" s="3" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1717" spans="1:2">
@@ -21354,7 +21695,7 @@
         <v>19</v>
       </c>
       <c r="B1790" s="3" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1791" spans="1:2">
@@ -21362,7 +21703,7 @@
         <v>1216</v>
       </c>
       <c r="B1791" s="3" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1792" spans="1:2">
@@ -21378,7 +21719,7 @@
         <v>17</v>
       </c>
       <c r="B1793" s="3" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1794" spans="1:2">
@@ -21410,7 +21751,7 @@
         <v>1625</v>
       </c>
       <c r="B1797" s="3" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1798" spans="1:2">
@@ -21426,7 +21767,7 @@
         <v>14</v>
       </c>
       <c r="B1799" s="3" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1800" spans="1:2">
@@ -21434,7 +21775,7 @@
         <v>13</v>
       </c>
       <c r="B1800" s="3" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1801" spans="1:2">
@@ -21578,7 +21919,7 @@
         <v>3</v>
       </c>
       <c r="B1818" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1819" spans="1:2">
@@ -21586,7 +21927,7 @@
         <v>4</v>
       </c>
       <c r="B1819" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1820" spans="1:2">
@@ -21594,7 +21935,7 @@
         <v>1341</v>
       </c>
       <c r="B1820" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1821" spans="1:2">
@@ -21602,7 +21943,7 @@
         <v>1340</v>
       </c>
       <c r="B1821" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1822" spans="1:2">
@@ -21610,7 +21951,7 @@
         <v>1184</v>
       </c>
       <c r="B1822" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1823" spans="1:2">
@@ -21618,7 +21959,7 @@
         <v>1090</v>
       </c>
       <c r="B1823" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1824" spans="1:2">
@@ -21626,7 +21967,7 @@
         <v>1714</v>
       </c>
       <c r="B1824" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1825" spans="1:2">
@@ -21634,7 +21975,7 @@
         <v>1321</v>
       </c>
       <c r="B1825" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1826" spans="1:2">
@@ -21642,7 +21983,7 @@
         <v>1769</v>
       </c>
       <c r="B1826" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1827" spans="1:2">
@@ -21650,7 +21991,7 @@
         <v>1602</v>
       </c>
       <c r="B1827" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1828" spans="1:2">
@@ -21674,7 +22015,7 @@
         <v>1</v>
       </c>
       <c r="B1830" s="3" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1831" spans="1:2">
@@ -21726,10 +22067,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1">
       <c r="A1" s="20" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
@@ -21739,74 +22080,74 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="8" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="8" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="8" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="8" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="8" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="8" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="8" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -21814,15 +22155,15 @@
         <v>187</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -21830,119 +22171,119 @@
         <v>1027</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="8" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="8" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="8" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="8" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="8" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="8" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="8" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="8" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="8" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="8" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="8" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="8" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -21950,71 +22291,71 @@
         <v>263</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="8" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="8" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="8" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="8" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="8" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="8" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="8" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -22022,207 +22363,207 @@
         <v>1020</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="8" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="9" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="8" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="8" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="8" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="8" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="8" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="8" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="8" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="8" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="8" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="8" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="8" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="8" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="8" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="8" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="10" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="10" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="10" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="10" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="10" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="10" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="11" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -22230,55 +22571,55 @@
         <v>66</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="8" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="8" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="8" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="8" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="11" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="8" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -22286,15 +22627,15 @@
         <v>43</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="8" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>2012</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -29923,12 +30264,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -29936,10 +30278,10 @@
         <v>1841</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -29947,10 +30289,10 @@
         <v>1882</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>2120</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -29958,10 +30300,10 @@
         <v>1853</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>2020</v>
+        <v>2101</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>2121</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -29969,10 +30311,10 @@
         <v>1853</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>2021</v>
+        <v>2102</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>2023</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -29980,21 +30322,21 @@
         <v>1853</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>2022</v>
+        <v>2119</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="23" t="s">
         <v>1853</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>2023</v>
+      <c r="B6" t="s">
+        <v>2149</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -30002,10 +30344,10 @@
         <v>1853</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>2024</v>
+        <v>2120</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -30013,10 +30355,10 @@
         <v>1853</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>2025</v>
+        <v>2121</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -30024,113 +30366,1398 @@
         <v>1853</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>2026</v>
+        <v>2148</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>2029</v>
+        <v>2150</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>2122</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>2120</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>2120</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>2028</v>
+        <v>2155</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>2120</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>2030</v>
+        <v>2021</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>2123</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>2031</v>
+        <v>2160</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>2124</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>2032</v>
+        <v>2161</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>2125</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>2033</v>
+        <v>2159</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>2125</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>2034</v>
+        <v>2103</v>
       </c>
       <c r="C18" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B39" s="23" t="s">
         <v>2125</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C68" s="42" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C69" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C71" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C72" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B74" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="23" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="23"/>
+      <c r="B76" s="23" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="23"/>
+      <c r="B77" s="23" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="23"/>
+      <c r="B78" s="23" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="23"/>
+      <c r="B79" s="23" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="23"/>
+      <c r="B80" s="23" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="23"/>
+      <c r="B81" s="23" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="23"/>
+      <c r="B82" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="23"/>
+      <c r="B83" s="23" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="23"/>
+      <c r="B84" s="23" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="23"/>
+      <c r="B85" s="23" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="23"/>
+      <c r="B86" s="23" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="23"/>
+      <c r="B87" s="23" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="23"/>
+      <c r="B88" s="23" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="23"/>
+      <c r="B89" s="23" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="23"/>
+      <c r="B90" s="23" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="23"/>
+      <c r="B91" s="23" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="23"/>
+      <c r="B92" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="23"/>
+      <c r="B93" s="23" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="23"/>
+      <c r="B94" s="23" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="23"/>
+      <c r="B95" s="23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="23"/>
+      <c r="B96" s="23" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="23"/>
+      <c r="B97" s="23" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="23"/>
+      <c r="B98" s="23" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="23"/>
+      <c r="B99" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="23"/>
+      <c r="B100" s="23" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="23"/>
+      <c r="B101" s="23" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="23"/>
+      <c r="B102" s="23" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="23"/>
+      <c r="B103" s="23" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C103" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="23"/>
+      <c r="B104" s="23" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C104" s="23" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="23"/>
+      <c r="B105" s="23" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="23"/>
+      <c r="B106" s="23" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="23"/>
+      <c r="B107" s="23" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C107" s="23" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="23"/>
+      <c r="B108" s="23" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C108" s="23" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="23"/>
+      <c r="B109" s="23" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C109" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="23"/>
+      <c r="B110" s="23" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C110" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="23"/>
+      <c r="B111" s="23" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C111" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="23"/>
+      <c r="B112" s="23" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C112" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="23"/>
+      <c r="B113" s="23" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C113" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="23"/>
+      <c r="B114" s="23" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C114" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="23"/>
+      <c r="B115" s="23" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="23"/>
+      <c r="B116" s="23" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="23"/>
+      <c r="B117" s="23" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="23"/>
+      <c r="B118" s="23" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="23"/>
+      <c r="B119" s="23" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C119" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="23"/>
+      <c r="B120" s="23" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="23"/>
+      <c r="B121" s="23" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="23"/>
+      <c r="B122" s="23" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="23"/>
+      <c r="B123" s="23" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C123" s="23" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="23"/>
+      <c r="B124" s="23" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="23"/>
+      <c r="B125" s="23" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C125" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="23"/>
+      <c r="B126" s="23" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="23"/>
+      <c r="B127" s="23" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C127" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="23"/>
+      <c r="B128" s="23" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C128" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="23"/>
+      <c r="B129" s="23" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C129" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="23"/>
+      <c r="B130" s="23" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C130" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="23"/>
+      <c r="B131" s="23" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C131" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="23"/>
+      <c r="B132" s="23" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C132" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="23"/>
+      <c r="B133" s="23" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C133" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="23"/>
+      <c r="B134" s="23" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C134" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="23"/>
+      <c r="B135" s="23" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C135" s="42" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="23"/>
+      <c r="B136" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C136" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="23"/>
+      <c r="B137" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C137" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="23"/>
+      <c r="B138" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C138" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="23"/>
+      <c r="B139" s="23" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C139" s="42" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="23"/>
+      <c r="B140" s="23" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C140" s="42" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="23"/>
+      <c r="B141" s="23" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C141" s="42" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="23"/>
+      <c r="B142" s="23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C142" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="23"/>
+      <c r="B143" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C143" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="23"/>
+      <c r="B144" s="23" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C144" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="23"/>
+      <c r="B145" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C145" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="23"/>
+      <c r="B146" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C146" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="23"/>
+      <c r="B147" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C147" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="23"/>
+      <c r="B148" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>2118</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30144,42 +31771,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>2035</v>
+        <v>2028</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>2044</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
-        <v>2036</v>
+        <v>2029</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>2037</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="26" t="s">
-        <v>2038</v>
+        <v>2031</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2039</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>2040</v>
+        <v>2033</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2041</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
-        <v>2042</v>
+        <v>2035</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>2043</v>
+        <v>2036</v>
       </c>
     </row>
   </sheetData>
@@ -30198,34 +31825,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>2045</v>
+        <v>2038</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>2046</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="26" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
     </row>
   </sheetData>
@@ -30235,142 +31862,581 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" style="30" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" s="34" t="s">
         <v>1841</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>2057</v>
+        <v>2045</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="31" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="31" customFormat="1">
       <c r="A2" s="36"/>
       <c r="B2" s="29" t="s">
-        <v>2060</v>
+        <v>2047</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="31" customFormat="1">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="31" customFormat="1">
       <c r="A3" s="36"/>
       <c r="B3" s="32" t="s">
-        <v>2068</v>
+        <v>2051</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="32" t="s">
         <v>1882</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>2019</v>
-      </c>
+      <c r="B4" s="32"/>
       <c r="C4" s="32" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>2173</v>
+      </c>
+      <c r="F4" s="31"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="32" t="s">
         <v>1853</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>2019</v>
-      </c>
+      <c r="B5" s="32"/>
       <c r="C5" s="32" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>2174</v>
+      </c>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="32" t="s">
         <v>1871</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>2019</v>
-      </c>
+      <c r="B6" s="32"/>
       <c r="C6" s="32" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>2175</v>
+      </c>
+      <c r="F6" s="31"/>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="32" t="s">
-        <v>2055</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>2019</v>
-      </c>
+        <v>1870</v>
+      </c>
+      <c r="B7" s="32"/>
       <c r="C7" s="32" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32" t="s">
-        <v>2058</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32" t="s">
-        <v>2059</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32" t="s">
-        <v>2064</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32" t="s">
-        <v>2066</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-    </row>
-    <row r="14" spans="1:3">
+        <v>2176</v>
+      </c>
+      <c r="F7" s="31"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="32" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="44" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F8" s="31"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="44" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="44" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F9" s="31"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="44" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="44" t="s">
+        <v>2181</v>
+      </c>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="44" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="44" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F11" s="31"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="44" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="44" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="44"/>
+      <c r="B13" s="30" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="44" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F14" s="31"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F15" s="31"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F16" s="31"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F18" s="31"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="32"/>
+      <c r="B19" s="44" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F19" s="31"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F20" s="31"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>2178</v>
+      </c>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="32"/>
+      <c r="B22" s="32" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="32"/>
+      <c r="B23" s="32" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="32"/>
+      <c r="B24" s="32" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="32"/>
+      <c r="B26" s="32" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="32"/>
+      <c r="B27" s="32" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="32"/>
+      <c r="B28" s="32" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="32"/>
+      <c r="B29" s="32" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="32"/>
+      <c r="B31" s="32" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="32"/>
+      <c r="B32" s="32" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="32"/>
+      <c r="B33" s="32" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="32"/>
+      <c r="B34" s="32" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="32"/>
+      <c r="B35" s="32" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="B36" s="30" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="32"/>
+      <c r="B37" s="32" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="32"/>
+      <c r="B38" s="32" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="32"/>
+      <c r="B39" s="32" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="32"/>
+      <c r="B40" s="32" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="32"/>
+      <c r="B41" s="32" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="32"/>
+      <c r="B42" s="32" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="32"/>
+      <c r="B43" s="32" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="32"/>
+      <c r="B44" s="32" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="32"/>
+      <c r="B45" s="32" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="32"/>
+      <c r="B46" s="32" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="32"/>
+      <c r="B47" s="32" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="32"/>
+      <c r="B48" s="44" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C48" s="44" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="32"/>
+      <c r="B49" s="32" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="32"/>
+      <c r="B50" s="32" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="32"/>
+      <c r="B51" s="44" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="32"/>
+      <c r="B52" s="32" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="32"/>
+      <c r="B53" s="32" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="32"/>
+      <c r="B54" s="32" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="32"/>
+      <c r="B55" s="43" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="32"/>
+      <c r="B56" s="43" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="32"/>
+      <c r="B57" s="43" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C57" s="44" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="32"/>
+      <c r="B58" s="32" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C58" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="32"/>
+      <c r="B59" s="32" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C59" s="44" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="32"/>
+      <c r="B60" s="32" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="32"/>
+      <c r="B61" s="32" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>2191</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30379,7 +32445,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="24" style="38" bestFit="1" customWidth="1"/>
@@ -30388,607 +32454,632 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="37" t="s">
-        <v>2070</v>
+        <v>2052</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>2071</v>
+        <v>2053</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>2072</v>
+        <v>2054</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>2073</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="39" t="s">
-        <v>2074</v>
+        <v>2056</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D2" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D2" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="39" t="s">
-        <v>2076</v>
+        <v>2057</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D3" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D3" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="41" t="s">
-        <v>2077</v>
+        <v>2058</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D4" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D4" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="41" t="s">
-        <v>2079</v>
+        <v>2060</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D5" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D5" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="39" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>2059</v>
       </c>
-      <c r="B6" s="39" t="s">
-        <v>2078</v>
-      </c>
       <c r="C6" s="39" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D6" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D6" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="41" t="s">
-        <v>2079</v>
+        <v>2060</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D7" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D7" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="39" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B8" s="39" t="s">
         <v>2059</v>
       </c>
-      <c r="B8" s="39" t="s">
-        <v>2078</v>
-      </c>
       <c r="C8" s="40" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D8" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D8" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="40" t="s">
-        <v>2080</v>
+        <v>2061</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>2081</v>
+        <v>2220</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>2080</v>
-      </c>
-      <c r="D9" s="40">
+        <v>2187</v>
+      </c>
+      <c r="D9" s="45">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="40" t="s">
-        <v>2082</v>
+        <v>2062</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>2081</v>
+        <v>2220</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>2082</v>
-      </c>
-      <c r="D10" s="40">
+        <v>2191</v>
+      </c>
+      <c r="D10" s="45">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="40" t="s">
-        <v>2083</v>
+        <v>2063</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>2081</v>
+        <v>2220</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>2083</v>
-      </c>
-      <c r="D11" s="40">
+        <v>2178</v>
+      </c>
+      <c r="D11" s="45">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="40" t="s">
-        <v>2084</v>
+        <v>2064</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>2081</v>
+        <v>2220</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2084</v>
-      </c>
-      <c r="D12" s="40">
+        <v>2134</v>
+      </c>
+      <c r="D12" s="45">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="39" t="s">
-        <v>2085</v>
+        <v>2065</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>2086</v>
-      </c>
-      <c r="D13" s="40">
+        <v>1853</v>
+      </c>
+      <c r="D13" s="45">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="39" t="s">
-        <v>2087</v>
+        <v>2066</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>2086</v>
-      </c>
-      <c r="D14" s="40">
+        <v>1853</v>
+      </c>
+      <c r="D14" s="45">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="39" t="s">
-        <v>2088</v>
+        <v>2067</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>2089</v>
-      </c>
-      <c r="D15" s="40">
+        <v>2221</v>
+      </c>
+      <c r="D15" s="45">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="39" t="s">
-        <v>2090</v>
+        <v>2068</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>2089</v>
-      </c>
-      <c r="D16" s="40">
+        <v>2221</v>
+      </c>
+      <c r="D16" s="45">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="41" t="s">
-        <v>2091</v>
+        <v>2069</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>2092</v>
-      </c>
-      <c r="D17" s="40">
+        <v>2222</v>
+      </c>
+      <c r="D17" s="45">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="40" t="s">
-        <v>2093</v>
+        <v>2070</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D18" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D18" s="45">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="41" t="s">
-        <v>2094</v>
+        <v>2071</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>2092</v>
-      </c>
-      <c r="D19" s="40">
+        <v>2222</v>
+      </c>
+      <c r="D19" s="45">
         <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="39" t="s">
-        <v>2095</v>
+        <v>2072</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>2096</v>
-      </c>
-      <c r="D20" s="40">
+        <v>2223</v>
+      </c>
+      <c r="D20" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="39" t="s">
-        <v>2097</v>
+        <v>2073</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>2096</v>
-      </c>
-      <c r="D21" s="40">
+        <v>2223</v>
+      </c>
+      <c r="D21" s="45">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="41" t="s">
-        <v>2098</v>
+        <v>2074</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D22" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D22" s="45">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="40" t="s">
-        <v>2099</v>
+        <v>2075</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D23" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D23" s="45">
         <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="39" t="s">
-        <v>2100</v>
+        <v>2076</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D24" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D24" s="45">
         <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="41" t="s">
-        <v>2101</v>
+        <v>2077</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D25" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D25" s="45">
         <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="40" t="s">
-        <v>2102</v>
+        <v>2078</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D26" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D26" s="45">
         <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="40" t="s">
-        <v>2103</v>
+        <v>2079</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D27" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D27" s="45">
         <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="39" t="s">
-        <v>2104</v>
+      <c r="A28" s="38" t="s">
+        <v>2181</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D28" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D28" s="45">
         <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="39" t="s">
-        <v>2105</v>
+        <v>2080</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D29" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D29" s="45">
         <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="40" t="s">
-        <v>2106</v>
+        <v>2081</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D30" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D30" s="45">
         <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="40" t="s">
-        <v>2107</v>
+        <v>2082</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D31" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D31" s="45">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="40" t="s">
-        <v>2108</v>
+        <v>2083</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D32" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D32" s="45">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="40" t="s">
-        <v>2109</v>
+        <v>2084</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D33" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D33" s="45">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="39" t="s">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D34" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D34" s="45">
         <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="39" t="s">
-        <v>2111</v>
+        <v>2086</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D35" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D35" s="45">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="39" t="s">
-        <v>2112</v>
+        <v>2087</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D36" s="40">
+        <v>1870</v>
+      </c>
+      <c r="D36" s="45">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="39" t="s">
-        <v>2113</v>
+        <v>2088</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D37" s="40">
+        <v>1870</v>
+      </c>
+      <c r="D37" s="45">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="39" t="s">
-        <v>2114</v>
+        <v>2089</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>2072</v>
+        <v>2219</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D38" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D38" s="45">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="39" t="s">
-        <v>2115</v>
+        <v>2090</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="39" t="s">
-        <v>2116</v>
+        <v>2091</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="39" t="s">
-        <v>2117</v>
+        <v>2092</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="40" t="s">
-        <v>2118</v>
+        <v>2093</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="40" t="s">
-        <v>2119</v>
+        <v>2094</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>2078</v>
-      </c>
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="40" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D44" s="40"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="46" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B45" s="40" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D45" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>